--- a/old results/side_by_side_comparison.xlsx
+++ b/old results/side_by_side_comparison.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X52"/>
+  <dimension ref="A1:R52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,70 +481,40 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>pred_RAG confusing</t>
+          <t>pred_+Reranker</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>correct_RAG confusing</t>
+          <t>correct_+Reranker</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>judgment_RAG confusing</t>
+          <t>judgment_+Reranker</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>pred_+Reranker</t>
+          <t>pred_BGE+RR</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>correct_+Reranker</t>
+          <t>correct_BGE+RR</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>judgment_+Reranker</t>
+          <t>judgment_BGE+RR</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>pred_Confusing+RR</t>
+          <t>n_correct</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>correct_Confusing+RR</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>judgment_Confusing+RR</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>pred_BGE+RR</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>correct_BGE+RR</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>judgment_BGE+RR</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>n_correct</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>n_configs</t>
         </is>
@@ -595,61 +565,35 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>PCIe 3.0 x16</t>
         </is>
       </c>
-      <c r="L2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
       <c r="O2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>wrong</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>PCIe 3.0 x16</t>
-        </is>
-      </c>
-      <c r="R2" t="b">
-        <v>1</v>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>PCIe</t>
-        </is>
-      </c>
-      <c r="U2" t="b">
-        <v>1</v>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>wrong</t>
-        </is>
-      </c>
-      <c r="W2" t="n">
-        <v>5</v>
-      </c>
-      <c r="X2" t="n">
-        <v>6</v>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>3</v>
+      </c>
+      <c r="R2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -697,61 +641,35 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>USB 2.0</t>
+          <t>USB 3.0</t>
         </is>
       </c>
       <c r="L3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>wrong</t>
+          <t>correct</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>USB 3.0</t>
+          <t>USB 3.1</t>
         </is>
       </c>
       <c r="O3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>correct</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>USB 2.0</t>
-        </is>
-      </c>
-      <c r="R3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>USB 3.1</t>
-        </is>
-      </c>
-      <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W3" t="n">
+      <c r="Q3" t="n">
         <v>2</v>
       </c>
-      <c r="X3" t="n">
-        <v>6</v>
+      <c r="R3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -812,7 +730,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>PCIe 3.0 x16</t>
+          <t>PCIe</t>
         </is>
       </c>
       <c r="O4" t="b">
@@ -820,40 +738,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>PCIe 3.0 x16</t>
-        </is>
-      </c>
-      <c r="R4" t="b">
-        <v>1</v>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>PCIe 3.0 x16</t>
-        </is>
-      </c>
-      <c r="U4" t="b">
-        <v>1</v>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W4" t="n">
-        <v>6</v>
-      </c>
-      <c r="X4" t="n">
-        <v>6</v>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -925,37 +817,11 @@
           <t>correct</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>PCIe 3.0</t>
-        </is>
-      </c>
-      <c r="R5" t="b">
-        <v>1</v>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>PCIe 3.0</t>
-        </is>
-      </c>
-      <c r="U5" t="b">
-        <v>1</v>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W5" t="n">
-        <v>5</v>
-      </c>
-      <c r="X5" t="n">
-        <v>6</v>
+      <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -1003,11 +869,11 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>PCIe 3.0 x16</t>
+          <t>PCIe</t>
         </is>
       </c>
       <c r="L6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1016,48 +882,22 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>PCIe</t>
+          <t>PCIe 3.0</t>
         </is>
       </c>
       <c r="O6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>acceptable</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>PCIe 3.0 x16</t>
-        </is>
-      </c>
-      <c r="R6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>PCIe 3.0 x16</t>
-        </is>
-      </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W6" t="n">
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
         <v>2</v>
       </c>
-      <c r="X6" t="n">
-        <v>6</v>
+      <c r="R6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -1105,61 +945,35 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>PCIe 3.0 x16</t>
+        </is>
+      </c>
+      <c r="L7" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>PCIe 3.0 x8</t>
         </is>
       </c>
-      <c r="L7" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>acceptable</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>PCIe 3.0 x16</t>
-        </is>
-      </c>
       <c r="O7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>correct</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>PCIe 3.0 x8</t>
-        </is>
-      </c>
-      <c r="R7" t="b">
-        <v>0</v>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>PCIe 3.0 x8</t>
-        </is>
-      </c>
-      <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W7" t="n">
+      <c r="Q7" t="n">
         <v>2</v>
       </c>
-      <c r="X7" t="n">
-        <v>6</v>
+      <c r="R7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -1231,37 +1045,11 @@
           <t>correct</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>SATA III</t>
-        </is>
-      </c>
-      <c r="R8" t="b">
-        <v>1</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>SATA III</t>
-        </is>
-      </c>
-      <c r="U8" t="b">
-        <v>1</v>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>5</v>
-      </c>
-      <c r="X8" t="n">
-        <v>6</v>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -1309,15 +1097,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>wrong</t>
+          <t>correct</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1333,37 +1121,11 @@
           <t>correct</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="R9" t="b">
-        <v>0</v>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>acceptable</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="U9" t="b">
-        <v>1</v>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W9" t="n">
+      <c r="Q9" t="n">
         <v>2</v>
       </c>
-      <c r="X9" t="n">
-        <v>6</v>
+      <c r="R9" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -1411,7 +1173,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="L10" t="b">
@@ -1424,48 +1186,22 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="R10" t="b">
-        <v>1</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U10" t="b">
-        <v>1</v>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W10" t="n">
-        <v>5</v>
-      </c>
-      <c r="X10" t="n">
-        <v>6</v>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1513,7 +1249,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="L11" t="b">
@@ -1521,12 +1257,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>wrong</t>
+          <t>correct</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42</t>
         </is>
       </c>
       <c r="O11" t="b">
@@ -1537,37 +1273,11 @@
           <t>correct</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="R11" t="b">
-        <v>0</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>acceptable</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="U11" t="b">
-        <v>1</v>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W11" t="n">
-        <v>4</v>
-      </c>
-      <c r="X11" t="n">
-        <v>6</v>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1615,61 +1325,35 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L12" t="b">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
           <t>20.8</t>
         </is>
       </c>
-      <c r="L12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
       <c r="O12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>wrong</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="R12" t="b">
-        <v>0</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wrong</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="U12" t="b">
-        <v>0</v>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>wrong</t>
-        </is>
-      </c>
-      <c r="W12" t="n">
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
         <v>2</v>
       </c>
-      <c r="X12" t="n">
-        <v>6</v>
+      <c r="R12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1717,15 +1401,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="L13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>wrong</t>
+          <t>correct</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1741,37 +1425,11 @@
           <t>correct</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="R13" t="b">
-        <v>1</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="U13" t="b">
-        <v>1</v>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W13" t="n">
-        <v>3</v>
-      </c>
-      <c r="X13" t="n">
-        <v>6</v>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -1819,61 +1477,35 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="L14" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
           <t>3.5</t>
         </is>
       </c>
-      <c r="L14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="O14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>wrong</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="R14" t="b">
-        <v>0</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wrong</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="U14" t="b">
-        <v>0</v>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>wrong</t>
-        </is>
-      </c>
-      <c r="W14" t="n">
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
         <v>2</v>
       </c>
-      <c r="X14" t="n">
-        <v>6</v>
+      <c r="R14" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -1921,20 +1553,20 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="L15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>correct</t>
+          <t>wrong</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>VALUE:7</t>
         </is>
       </c>
       <c r="O15" t="b">
@@ -1945,37 +1577,11 @@
           <t>wrong</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="R15" t="b">
-        <v>0</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wrong</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="U15" t="b">
-        <v>0</v>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>wrong</t>
-        </is>
-      </c>
-      <c r="W15" t="n">
-        <v>2</v>
-      </c>
-      <c r="X15" t="n">
-        <v>6</v>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -2036,48 +1642,22 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>220S</t>
+          <t>Intenso HIGH SSD</t>
         </is>
       </c>
       <c r="O16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>220S</t>
-        </is>
-      </c>
-      <c r="R16" t="b">
-        <v>1</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>SSD220</t>
-        </is>
-      </c>
-      <c r="U16" t="b">
-        <v>0</v>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>wrong</t>
-        </is>
-      </c>
-      <c r="W16" t="n">
-        <v>4</v>
-      </c>
-      <c r="X16" t="n">
-        <v>6</v>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -2133,53 +1713,27 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>acceptable</t>
+          <t>correct</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Ultimate SU800</t>
+          <t>Ultimate</t>
         </is>
       </c>
       <c r="O17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Ultimate SU800</t>
-        </is>
-      </c>
-      <c r="R17" t="b">
-        <v>1</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Ultimate SU800</t>
-        </is>
-      </c>
-      <c r="U17" t="b">
-        <v>1</v>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W17" t="n">
-        <v>6</v>
-      </c>
-      <c r="X17" t="n">
-        <v>6</v>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>3</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -2227,20 +1781,20 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>IronWolf 110</t>
+          <t>Barracuda Q1</t>
         </is>
       </c>
       <c r="L18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>correct</t>
+          <t>wrong</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Barracuda Q1</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="O18" t="b">
@@ -2251,37 +1805,11 @@
           <t>wrong</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>IronWolf 110</t>
-        </is>
-      </c>
-      <c r="R18" t="b">
-        <v>1</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Nytro 1351</t>
-        </is>
-      </c>
-      <c r="U18" t="b">
-        <v>0</v>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>wrong</t>
-        </is>
-      </c>
-      <c r="W18" t="n">
-        <v>2</v>
-      </c>
-      <c r="X18" t="n">
-        <v>6</v>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -2329,7 +1857,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>HPE 2TB SATA LFF</t>
+          <t>801882-B21</t>
         </is>
       </c>
       <c r="L19" t="b">
@@ -2353,37 +1881,11 @@
           <t>wrong</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>HPE 1TB SATA LFF</t>
-        </is>
-      </c>
-      <c r="R19" t="b">
-        <v>0</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wrong</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>801882-B21</t>
-        </is>
-      </c>
-      <c r="U19" t="b">
-        <v>0</v>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>wrong</t>
-        </is>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>6</v>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -2431,15 +1933,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>MQ04ABD200</t>
+          <t>L200</t>
         </is>
       </c>
       <c r="L20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>wrong</t>
+          <t>correct</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2455,37 +1957,11 @@
           <t>correct</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>L200</t>
-        </is>
-      </c>
-      <c r="R20" t="b">
-        <v>1</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>L200</t>
-        </is>
-      </c>
-      <c r="U20" t="b">
-        <v>1</v>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W20" t="n">
-        <v>3</v>
-      </c>
-      <c r="X20" t="n">
-        <v>6</v>
+      <c r="Q20" t="n">
+        <v>2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -2557,37 +2033,11 @@
           <t>correct</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>GV-N3080GAMING OC-10GD</t>
-        </is>
-      </c>
-      <c r="R21" t="b">
-        <v>1</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>GV-N3080GAMING OC-10GD</t>
-        </is>
-      </c>
-      <c r="U21" t="b">
-        <v>1</v>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W21" t="n">
-        <v>5</v>
-      </c>
-      <c r="X21" t="n">
-        <v>6</v>
+      <c r="Q21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -2659,37 +2109,11 @@
           <t>correct</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>CSSD-F960GBMP510</t>
-        </is>
-      </c>
-      <c r="R22" t="b">
-        <v>1</v>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="U22" t="b">
-        <v>0</v>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>wrong</t>
-        </is>
-      </c>
-      <c r="W22" t="n">
-        <v>5</v>
-      </c>
-      <c r="X22" t="n">
-        <v>6</v>
+      <c r="Q22" t="n">
+        <v>4</v>
+      </c>
+      <c r="R22" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -2737,15 +2161,15 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>90YV0CV2-M0NA00</t>
         </is>
       </c>
       <c r="L23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>wrong</t>
+          <t>correct</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2761,37 +2185,11 @@
           <t>correct</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>90YV0CV2-M0NA00</t>
-        </is>
-      </c>
-      <c r="R23" t="b">
-        <v>1</v>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>90YV0CV0-M0NA00</t>
-        </is>
-      </c>
-      <c r="U23" t="b">
-        <v>0</v>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W23" t="n">
+      <c r="Q23" t="n">
         <v>3</v>
       </c>
-      <c r="X23" t="n">
-        <v>6</v>
+      <c r="R23" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -2839,22 +2237,22 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t>GeForce GTX 1660 OC</t>
+        </is>
+      </c>
+      <c r="L24" t="b">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="L24" t="b">
-        <v>0</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>wrong</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>GeForce GTX 1660 OC</t>
-        </is>
-      </c>
       <c r="O24" t="b">
         <v>0</v>
       </c>
@@ -2863,37 +2261,11 @@
           <t>wrong</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>GV-N1660OC-6GD</t>
-        </is>
-      </c>
-      <c r="R24" t="b">
-        <v>0</v>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>GV-N166TSL-6GD</t>
-        </is>
-      </c>
-      <c r="U24" t="b">
-        <v>0</v>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>6</v>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -2941,7 +2313,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>GTX 1660 SUPER GAMING X</t>
+          <t>912-V375-040</t>
         </is>
       </c>
       <c r="L25" t="b">
@@ -2949,7 +2321,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>wrong</t>
+          <t>correct</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2965,37 +2337,11 @@
           <t>correct</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>912-V375-040</t>
-        </is>
-      </c>
-      <c r="R25" t="b">
-        <v>0</v>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>912-V375-040</t>
-        </is>
-      </c>
-      <c r="U25" t="b">
-        <v>0</v>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W25" t="n">
-        <v>1</v>
-      </c>
-      <c r="X25" t="n">
-        <v>6</v>
+      <c r="Q25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -3043,7 +2389,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>ROG-STRIX-RTX2060S-O8G-GAMING</t>
+          <t>90YV0C90-M0NA00</t>
         </is>
       </c>
       <c r="L26" t="b">
@@ -3051,53 +2397,27 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>wrong</t>
+          <t>correct</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>90YV0C90-M0NA00</t>
+          <t>90YV0DQ0-M0NA00</t>
         </is>
       </c>
       <c r="O26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>correct</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>ROG-STRIX-RTX2060S-O8G-GAMING</t>
-        </is>
-      </c>
-      <c r="R26" t="b">
-        <v>0</v>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wrong</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>ROG Strix GeForce RTX 2070 Super Advance Gaming</t>
-        </is>
-      </c>
-      <c r="U26" t="b">
-        <v>0</v>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>wrong</t>
-        </is>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>6</v>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -3145,61 +2465,35 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>AGAMMIXS11P-512GT-C</t>
+          <t>AGAMMIXS11P-1TT-C</t>
         </is>
       </c>
       <c r="L27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>wrong</t>
+          <t>correct</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>AGAMMIXS11P-1TT-C</t>
+          <t>GAMMIX Gaming SSD S11 Pro Series</t>
         </is>
       </c>
       <c r="O27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>AGAMMIXS11P-1TT-C</t>
-        </is>
-      </c>
-      <c r="R27" t="b">
-        <v>1</v>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>AGAMMIXS11P-1TT-C</t>
-        </is>
-      </c>
-      <c r="U27" t="b">
-        <v>1</v>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W27" t="n">
-        <v>3</v>
-      </c>
-      <c r="X27" t="n">
-        <v>6</v>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -3247,15 +2541,15 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Radeon RX 5600 XT GAMING OC</t>
+          <t>GV-R56XTGAMING OC-6GD</t>
         </is>
       </c>
       <c r="L28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>wrong</t>
+          <t>correct</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3271,37 +2565,11 @@
           <t>correct</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>GV-R56XTGAMING OC-6GD</t>
-        </is>
-      </c>
-      <c r="R28" t="b">
-        <v>1</v>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>GV-R56XTGAMING OC-6GD</t>
-        </is>
-      </c>
-      <c r="U28" t="b">
-        <v>1</v>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W28" t="n">
-        <v>3</v>
-      </c>
-      <c r="X28" t="n">
-        <v>6</v>
+      <c r="Q28" t="n">
+        <v>2</v>
+      </c>
+      <c r="R28" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -3373,37 +2641,11 @@
           <t>correct</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>100-506008</t>
-        </is>
-      </c>
-      <c r="R29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>100-506008</t>
-        </is>
-      </c>
-      <c r="U29" t="b">
-        <v>1</v>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W29" t="n">
-        <v>5</v>
-      </c>
-      <c r="X29" t="n">
-        <v>6</v>
+      <c r="Q29" t="n">
+        <v>3</v>
+      </c>
+      <c r="R29" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -3451,15 +2693,15 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>NE6166T018J9-161F</t>
+          <t>NE6166SS18J9-161F</t>
         </is>
       </c>
       <c r="L30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>wrong</t>
+          <t>correct</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3475,37 +2717,11 @@
           <t>correct</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>NE6166S018J9-1160A</t>
-        </is>
-      </c>
-      <c r="R30" t="b">
-        <v>0</v>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>NE6166SS18J9-161F</t>
-        </is>
-      </c>
-      <c r="U30" t="b">
-        <v>1</v>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W30" t="n">
+      <c r="Q30" t="n">
         <v>2</v>
       </c>
-      <c r="X30" t="n">
-        <v>6</v>
+      <c r="R30" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -3577,37 +2793,11 @@
           <t>correct</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>801882-B21</t>
-        </is>
-      </c>
-      <c r="R31" t="b">
-        <v>1</v>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>801882-B21</t>
-        </is>
-      </c>
-      <c r="U31" t="b">
-        <v>1</v>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W31" t="n">
-        <v>5</v>
-      </c>
-      <c r="X31" t="n">
-        <v>6</v>
+      <c r="Q31" t="n">
+        <v>3</v>
+      </c>
+      <c r="R31" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -3679,37 +2869,11 @@
           <t>correct</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>3480</t>
-        </is>
-      </c>
-      <c r="R32" t="b">
-        <v>1</v>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>3480</t>
-        </is>
-      </c>
-      <c r="U32" t="b">
-        <v>1</v>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W32" t="n">
-        <v>5</v>
-      </c>
-      <c r="X32" t="n">
-        <v>6</v>
+      <c r="Q32" t="n">
+        <v>3</v>
+      </c>
+      <c r="R32" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -3757,7 +2921,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>226.0</t>
         </is>
       </c>
       <c r="L33" t="b">
@@ -3781,37 +2945,11 @@
           <t>correct</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>226.0</t>
-        </is>
-      </c>
-      <c r="R33" t="b">
-        <v>1</v>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>226.0</t>
-        </is>
-      </c>
-      <c r="U33" t="b">
-        <v>1</v>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W33" t="n">
-        <v>5</v>
-      </c>
-      <c r="X33" t="n">
-        <v>6</v>
+      <c r="Q33" t="n">
+        <v>3</v>
+      </c>
+      <c r="R33" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -3883,37 +3021,11 @@
           <t>correct</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="R34" t="b">
-        <v>1</v>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="U34" t="b">
-        <v>1</v>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W34" t="n">
-        <v>5</v>
-      </c>
-      <c r="X34" t="n">
-        <v>6</v>
+      <c r="Q34" t="n">
+        <v>3</v>
+      </c>
+      <c r="R34" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -3961,7 +3073,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>550</t>
         </is>
       </c>
       <c r="L35" t="b">
@@ -3974,7 +3086,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>555</t>
         </is>
       </c>
       <c r="O35" t="b">
@@ -3985,37 +3097,11 @@
           <t>correct</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="R35" t="b">
-        <v>1</v>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="U35" t="b">
-        <v>1</v>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W35" t="n">
-        <v>4</v>
-      </c>
-      <c r="X35" t="n">
-        <v>6</v>
+      <c r="Q35" t="n">
+        <v>2</v>
+      </c>
+      <c r="R35" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -4063,61 +3149,35 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L36" t="b">
+        <v>0</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="L36" t="b">
-        <v>1</v>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
       <c r="O36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>wrong</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="R36" t="b">
-        <v>0</v>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wrong</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="U36" t="b">
-        <v>0</v>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>wrong</t>
-        </is>
-      </c>
-      <c r="W36" t="n">
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
         <v>2</v>
       </c>
-      <c r="X36" t="n">
-        <v>6</v>
+      <c r="R36" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -4165,7 +3225,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>540</t>
         </is>
       </c>
       <c r="L37" t="b">
@@ -4173,7 +3233,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>wrong</t>
+          <t>correct</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4189,37 +3249,11 @@
           <t>correct</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
-      <c r="R37" t="b">
-        <v>1</v>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
-      <c r="U37" t="b">
-        <v>1</v>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W37" t="n">
-        <v>5</v>
-      </c>
-      <c r="X37" t="n">
-        <v>6</v>
+      <c r="Q37" t="n">
+        <v>3</v>
+      </c>
+      <c r="R37" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="38">
@@ -4291,37 +3325,11 @@
           <t>correct</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
-      <c r="R38" t="b">
-        <v>1</v>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
-      <c r="U38" t="b">
-        <v>1</v>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W38" t="n">
-        <v>5</v>
-      </c>
-      <c r="X38" t="n">
-        <v>6</v>
+      <c r="Q38" t="n">
+        <v>3</v>
+      </c>
+      <c r="R38" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -4393,37 +3401,11 @@
           <t>correct</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
-      <c r="R39" t="b">
-        <v>1</v>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
-      <c r="U39" t="b">
-        <v>1</v>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W39" t="n">
-        <v>5</v>
-      </c>
-      <c r="X39" t="n">
-        <v>6</v>
+      <c r="Q39" t="n">
+        <v>3</v>
+      </c>
+      <c r="R39" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -4495,37 +3477,11 @@
           <t>correct</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
-      <c r="R40" t="b">
-        <v>1</v>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="U40" t="b">
-        <v>0</v>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>wrong</t>
-        </is>
-      </c>
-      <c r="W40" t="n">
-        <v>3</v>
-      </c>
-      <c r="X40" t="n">
-        <v>6</v>
+      <c r="Q40" t="n">
+        <v>2</v>
+      </c>
+      <c r="R40" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -4573,7 +3529,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>560</t>
         </is>
       </c>
       <c r="L41" t="b">
@@ -4586,48 +3542,22 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>VALUE:530</t>
         </is>
       </c>
       <c r="O41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
-      <c r="R41" t="b">
-        <v>1</v>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
-      <c r="U41" t="b">
-        <v>1</v>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W41" t="n">
-        <v>4</v>
-      </c>
-      <c r="X41" t="n">
-        <v>6</v>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>1</v>
+      </c>
+      <c r="R41" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -4675,15 +3605,15 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>433</t>
         </is>
       </c>
       <c r="L42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>wrong</t>
+          <t>correct</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4699,37 +3629,11 @@
           <t>correct</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
-      <c r="R42" t="b">
-        <v>1</v>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="U42" t="b">
-        <v>0</v>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>wrong</t>
-        </is>
-      </c>
-      <c r="W42" t="n">
+      <c r="Q42" t="n">
         <v>2</v>
       </c>
-      <c r="X42" t="n">
-        <v>6</v>
+      <c r="R42" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -4777,15 +3681,15 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>127</t>
         </is>
       </c>
       <c r="L43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>wrong</t>
+          <t>correct</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4801,37 +3705,11 @@
           <t>correct</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="R43" t="b">
-        <v>0</v>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>acceptable</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="U43" t="b">
-        <v>1</v>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W43" t="n">
+      <c r="Q43" t="n">
         <v>3</v>
       </c>
-      <c r="X43" t="n">
-        <v>6</v>
+      <c r="R43" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="44">
@@ -4879,15 +3757,15 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>130.9</t>
         </is>
       </c>
       <c r="L44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>wrong</t>
+          <t>correct</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4903,37 +3781,11 @@
           <t>correct</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="R44" t="b">
-        <v>0</v>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>acceptable</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>130.9</t>
-        </is>
-      </c>
-      <c r="U44" t="b">
-        <v>1</v>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W44" t="n">
+      <c r="Q44" t="n">
         <v>3</v>
       </c>
-      <c r="X44" t="n">
-        <v>6</v>
+      <c r="R44" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -4981,61 +3833,35 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L45" t="b">
+        <v>0</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
           <t>87.9</t>
         </is>
       </c>
-      <c r="L45" t="b">
-        <v>1</v>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
       <c r="O45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>wrong</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="R45" t="b">
-        <v>1</v>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="U45" t="b">
-        <v>0</v>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>wrong</t>
-        </is>
-      </c>
-      <c r="W45" t="n">
-        <v>3</v>
-      </c>
-      <c r="X45" t="n">
-        <v>6</v>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>2</v>
+      </c>
+      <c r="R45" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="46">
@@ -5083,7 +3909,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>VALUE:UNKNOWN</t>
         </is>
       </c>
       <c r="L46" t="b">
@@ -5096,7 +3922,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>VALUE:UNKNOWN</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="O46" t="b">
@@ -5107,37 +3933,11 @@
           <t>wrong</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>57.3</t>
-        </is>
-      </c>
-      <c r="R46" t="b">
-        <v>1</v>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="U46" t="b">
-        <v>0</v>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>wrong</t>
-        </is>
-      </c>
-      <c r="W46" t="n">
-        <v>1</v>
-      </c>
-      <c r="X46" t="n">
-        <v>6</v>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="47">
@@ -5185,61 +3985,35 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L47" t="b">
+        <v>0</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="L47" t="b">
-        <v>1</v>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
       <c r="O47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>wrong</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="R47" t="b">
-        <v>0</v>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wrong</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="U47" t="b">
-        <v>0</v>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>wrong</t>
-        </is>
-      </c>
-      <c r="W47" t="n">
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
         <v>2</v>
       </c>
-      <c r="X47" t="n">
-        <v>6</v>
+      <c r="R47" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -5311,37 +4085,11 @@
           <t>correct</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="R48" t="b">
-        <v>1</v>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="U48" t="b">
-        <v>1</v>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W48" t="n">
-        <v>5</v>
-      </c>
-      <c r="X48" t="n">
-        <v>6</v>
+      <c r="Q48" t="n">
+        <v>3</v>
+      </c>
+      <c r="R48" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -5389,61 +4137,35 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L49" t="b">
+        <v>0</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
           <t>520</t>
         </is>
       </c>
-      <c r="L49" t="b">
-        <v>1</v>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
       <c r="O49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>wrong</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="R49" t="b">
-        <v>1</v>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="U49" t="b">
-        <v>1</v>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W49" t="n">
-        <v>4</v>
-      </c>
-      <c r="X49" t="n">
-        <v>6</v>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>2</v>
+      </c>
+      <c r="R49" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -5504,48 +4226,22 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="O50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="R50" t="b">
-        <v>0</v>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wrong</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>520</t>
-        </is>
-      </c>
-      <c r="U50" t="b">
-        <v>1</v>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W50" t="n">
-        <v>4</v>
-      </c>
-      <c r="X50" t="n">
-        <v>6</v>
+          <t>wrong</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>2</v>
+      </c>
+      <c r="R50" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="51">
@@ -5617,37 +4313,11 @@
           <t>correct</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="R51" t="b">
-        <v>1</v>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="U51" t="b">
-        <v>1</v>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W51" t="n">
-        <v>5</v>
-      </c>
-      <c r="X51" t="n">
-        <v>6</v>
+      <c r="Q51" t="n">
+        <v>3</v>
+      </c>
+      <c r="R51" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -5695,20 +4365,20 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="L52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>correct</t>
+          <t>wrong</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>VALUE:530</t>
         </is>
       </c>
       <c r="O52" t="b">
@@ -5719,37 +4389,11 @@
           <t>wrong</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
-      <c r="R52" t="b">
-        <v>1</v>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
-      <c r="U52" t="b">
-        <v>1</v>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="W52" t="n">
-        <v>4</v>
-      </c>
-      <c r="X52" t="n">
-        <v>6</v>
+      <c r="Q52" t="n">
+        <v>1</v>
+      </c>
+      <c r="R52" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
